--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,31 +812,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R3" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,35 +933,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R4" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,6 +1034,363 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125388704</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nol, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>329792</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419546</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125388968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nol, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>330272</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6419666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125388932</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56856</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nol, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330263</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6419694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,35 +812,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R3" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +928,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R4" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,6 +1018,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383185</v>
+        <v>125383162</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329858</v>
+        <v>329883</v>
       </c>
       <c r="R2" t="n">
-        <v>6419489</v>
+        <v>6419461</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,17 +771,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande samt hörde den.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383816</v>
+        <v>125383185</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -836,7 +832,11 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329792</v>
+        <v>329858</v>
       </c>
       <c r="R3" t="n">
-        <v>6419545</v>
+        <v>6419489</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande samt hörde den.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,35 +933,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R4" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125388704</v>
+        <v>125388968</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,31 +1049,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329792</v>
+        <v>330272</v>
       </c>
       <c r="R5" t="n">
-        <v>6419546</v>
+        <v>6419666</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1139,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125388968</v>
+        <v>125388704</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,35 +1169,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,13 +1201,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330272</v>
+        <v>329792</v>
       </c>
       <c r="R6" t="n">
-        <v>6419666</v>
+        <v>6419546</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,6 +1255,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R2" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +773,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383185</v>
+        <v>125383162</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>97147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +803,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329858</v>
+        <v>329883</v>
       </c>
       <c r="R3" t="n">
-        <v>6419489</v>
+        <v>6419461</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,17 +887,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande samt hörde den.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383816</v>
+        <v>125383185</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,7 +948,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329792</v>
+        <v>329858</v>
       </c>
       <c r="R4" t="n">
-        <v>6419545</v>
+        <v>6419489</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande samt hörde den.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125388968</v>
+        <v>125388932</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56949</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330272</v>
+        <v>330263</v>
       </c>
       <c r="R5" t="n">
-        <v>6419666</v>
+        <v>6419694</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1160,7 @@
         <v>125388704</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125388932</v>
+        <v>125388968</v>
       </c>
       <c r="B7" t="n">
-        <v>56856</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330263</v>
+        <v>330272</v>
       </c>
       <c r="R7" t="n">
-        <v>6419694</v>
+        <v>6419666</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>97147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R2" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383162</v>
+        <v>125383185</v>
       </c>
       <c r="B3" t="n">
-        <v>97147</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329883</v>
+        <v>329858</v>
       </c>
       <c r="R3" t="n">
-        <v>6419461</v>
+        <v>6419489</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,13 +892,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande samt hörde den.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,7 +921,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383185</v>
+        <v>125383816</v>
       </c>
       <c r="B4" t="n">
         <v>57632</v>
@@ -948,11 +957,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329858</v>
+        <v>329792</v>
       </c>
       <c r="R4" t="n">
-        <v>6419489</v>
+        <v>6419545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande samt hörde den.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>125383162</v>
       </c>
       <c r="B3" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>125388704</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>97209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R2" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,42 +791,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B3" t="n">
-        <v>97209</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R3" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B2" t="n">
-        <v>97209</v>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R2" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,38 +786,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>97212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R3" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +883,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>125388704</v>
       </c>
       <c r="B5" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95934</v>
+        <v>95937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>125383162</v>
       </c>
       <c r="B3" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>125388704</v>
       </c>
       <c r="B5" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383816</v>
+        <v>125383162</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329792</v>
+        <v>329883</v>
       </c>
       <c r="R2" t="n">
-        <v>6419545</v>
+        <v>6419461</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,42 +791,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383162</v>
+        <v>125383816</v>
       </c>
       <c r="B3" t="n">
-        <v>97216</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329883</v>
+        <v>329792</v>
       </c>
       <c r="R3" t="n">
-        <v>6419461</v>
+        <v>6419545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>125388704</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>125726952</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125727349</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>125726977</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +1920,589 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126258368</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97221</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lilla Sandsjön, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>329884</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6419575</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126258262</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sandsjöhult, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>330236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6419642</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126258434</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sandsjöhult, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>329803</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6419545</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126258223</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sandsjöhult, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>330320</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6419625</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126258445</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sandsjöhult, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>329892</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6419542</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hörd flygande.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126258368</v>
       </c>
       <c r="B13" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>125726952</v>
       </c>
       <c r="B9" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125727349</v>
       </c>
       <c r="B10" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>125726977</v>
       </c>
       <c r="B11" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126258368</v>
       </c>
       <c r="B13" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>126258262</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>126258434</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126258223</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>126258445</v>
       </c>
       <c r="B17" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1367,7 +1367,7 @@
         <v>125727012</v>
       </c>
       <c r="B8" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126258368</v>
       </c>
       <c r="B13" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -1925,7 +1925,7 @@
         <v>126258368</v>
       </c>
       <c r="B13" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>126258262</v>
       </c>
       <c r="B14" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>126258434</v>
       </c>
       <c r="B15" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>126258223</v>
       </c>
       <c r="B16" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>126258445</v>
       </c>
       <c r="B17" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125383162</v>
+        <v>125727012</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Sandsjödal, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329883</v>
+        <v>330085</v>
       </c>
       <c r="R2" t="n">
-        <v>6419461</v>
+        <v>6419607</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125383816</v>
+        <v>125383185</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,7 +818,11 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329792</v>
+        <v>329858</v>
       </c>
       <c r="R3" t="n">
-        <v>6419545</v>
+        <v>6419489</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår efter födosökande samt hörde den.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,14 +907,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125383185</v>
+        <v>125383816</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,11 +938,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329858</v>
+        <v>329792</v>
       </c>
       <c r="R4" t="n">
-        <v>6419489</v>
+        <v>6419545</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår efter födosökande samt hörde den.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125388704</v>
+        <v>125388968</v>
       </c>
       <c r="B5" t="n">
-        <v>97217</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,27 +1029,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329792</v>
+        <v>330272</v>
       </c>
       <c r="R5" t="n">
-        <v>6419546</v>
+        <v>6419666</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,14 +1133,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125388968</v>
+        <v>125726952</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1165,25 +1164,21 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Sandsjödal, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330272</v>
+        <v>330201</v>
       </c>
       <c r="R6" t="n">
-        <v>6419666</v>
+        <v>6419677</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,22 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125388932</v>
+        <v>125726977</v>
       </c>
       <c r="B7" t="n">
-        <v>56958</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,16 +1255,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,25 +1275,21 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nol, Vg</t>
+          <t>Sandsjödal, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330263</v>
+        <v>330269</v>
       </c>
       <c r="R7" t="n">
-        <v>6419694</v>
+        <v>6419666</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,22 +1313,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125727012</v>
+        <v>125727283</v>
       </c>
       <c r="B8" t="n">
-        <v>95955</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,27 +1366,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330085</v>
+        <v>330027</v>
       </c>
       <c r="R8" t="n">
-        <v>6419607</v>
+        <v>6419608</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1448,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,14 +1466,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125726952</v>
+        <v>125727349</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1515,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330201</v>
+        <v>330144</v>
       </c>
       <c r="R9" t="n">
-        <v>6419677</v>
+        <v>6419650</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,14 +1577,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125727349</v>
+        <v>126258445</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1615,24 +1605,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandsjödal, Vg</t>
+          <t>Sandsjöhult, norr om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330144</v>
+        <v>329892</v>
       </c>
       <c r="R10" t="n">
-        <v>6419650</v>
+        <v>6419542</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,22 +1654,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hörd flygande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,39 +1689,39 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125726977</v>
+        <v>125388932</v>
       </c>
       <c r="B11" t="n">
-        <v>57653</v>
+        <v>57258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1729,21 +1732,25 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandsjödal, Vg</t>
+          <t>Nol, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330269</v>
+        <v>330263</v>
       </c>
       <c r="R11" t="n">
-        <v>6419666</v>
+        <v>6419694</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,22 +1774,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,53 +1816,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125727421</v>
+        <v>126258299</v>
       </c>
       <c r="B12" t="n">
-        <v>30129</v>
+        <v>58238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>200985</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandsjödal, Vg</t>
+          <t>Sandsjöhult, norr om, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330205</v>
+        <v>330117</v>
       </c>
       <c r="R12" t="n">
-        <v>6419700</v>
+        <v>6419645</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,22 +1893,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,29 +1917,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126258368</v>
+        <v>126258223</v>
       </c>
       <c r="B13" t="n">
-        <v>97239</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1933,38 +1946,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla Sandsjön, söder om, Vg</t>
+          <t>Sandsjöhult, norr om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>329884</v>
+        <v>330320</v>
       </c>
       <c r="R13" t="n">
-        <v>6419575</v>
+        <v>6419625</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,18 +2015,27 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2027,7 +2057,7 @@
         <v>126258262</v>
       </c>
       <c r="B14" t="n">
-        <v>58027</v>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2176,7 @@
         <v>126258434</v>
       </c>
       <c r="B15" t="n">
-        <v>58027</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126258223</v>
+        <v>126258455</v>
       </c>
       <c r="B16" t="n">
-        <v>58027</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,13 +2339,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>330320</v>
+        <v>329983</v>
       </c>
       <c r="R16" t="n">
-        <v>6419625</v>
+        <v>6419565</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,60 +2411,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126258445</v>
+        <v>125727421</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>30288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>200985</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandsjöhult, norr om, Vg</t>
+          <t>Sandsjödal, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>329892</v>
+        <v>330205</v>
       </c>
       <c r="R17" t="n">
-        <v>6419542</v>
+        <v>6419700</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,27 +2481,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hörd flygande.</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,21 +2505,352 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125383162</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nol, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>329883</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6419461</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125388704</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nol, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>329792</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6419546</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126258368</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lilla Sandsjön, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>329884</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6419575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24162-2025 artfynd.xlsx
+++ b/artfynd/A 24162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125727012</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125383185</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125383816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125388968</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125726952</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125726977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125727283</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,6 +1614,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125727349</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258445</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,6 +1863,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125388932</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1932,6 +1987,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258299</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258223</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258262</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2289,6 +2359,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258455</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2521,6 +2601,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125727421</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2637,6 +2722,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125383162</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2749,6 +2839,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125388704</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2851,8 +2946,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126258368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>